--- a/addons/TinyTools/ConfigGenerator/EquipSetConfig.xlsx
+++ b/addons/TinyTools/ConfigGenerator/EquipSetConfig.xlsx
@@ -497,7 +497,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="n">
         <v>1</v>
@@ -644,7 +643,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DoT 流：叠毒/灼烧的伤害与层数上限</t>
+          <t>DoT 流：叠毒/灼烧的伤害与叠层速度（每次额外 +1 层）</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -657,7 +656,7 @@
         <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
